--- a/artfynd/A 46300-2025 artfynd.xlsx
+++ b/artfynd/A 46300-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120756548</v>
+        <v>120756453</v>
       </c>
       <c r="B2" t="n">
-        <v>97025</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57890</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,48 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100082</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>NV om Strängsered, Vg</t>
+          <t>NV om Strängsered, Strängsered, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419697</v>
+        <v>419990</v>
       </c>
       <c r="R2" t="n">
-        <v>6406437</v>
+        <v>6406362</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +744,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Kom lågt från öst.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,19 +773,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Andreas Ekedahl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Andreas Ekedahl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -803,15 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120756453</v>
+        <v>120756548</v>
       </c>
       <c r="B3" t="n">
-        <v>57256</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,41 +806,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100082</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NV om Strängsered, Strängsered, Vg</t>
+          <t>NV om Strängsered, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419990</v>
+        <v>419697</v>
       </c>
       <c r="R3" t="n">
-        <v>6406362</v>
+        <v>6406437</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,27 +871,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Kom lågt från öst.</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,18 +895,19 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Andreas Ekedahl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Andreas Ekedahl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
